--- a/ExcelTool/LubanTools/DataTables/Datas/TutorialStepData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/TutorialStepData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DBDF9BB-4B35-4AB8-916C-A6B3AE5CB1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCC9928-128E-4992-9BA5-C2929377B67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4450" yWindow="2240" windowWidth="44100" windowHeight="18570" xr2:uid="{2289B342-06D8-41FC-9CAA-D2C17ACF82D3}"/>
+    <workbookView xWindow="-16370" yWindow="7300" windowWidth="44100" windowHeight="18570" xr2:uid="{2289B342-06D8-41FC-9CAA-D2C17ACF82D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -209,37 +209,41 @@
     <t>UIPath</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>FitTarget</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>ClickTarget</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>Arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,20,20,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>MainUI</t>
-  </si>
-  <si>
-    <t>UIMask/DownButtons/BagButton</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>FitTarget</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>0,0,0,0</t>
-  </si>
-  <si>
-    <t>Auto</t>
-  </si>
-  <si>
-    <t>Finger</t>
-  </si>
-  <si>
-    <t>ClickTarget</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>模板行:点亮背包按钮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模板行:高亮大厅的背包按钮,点中它这段引导就结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIMask/MenuButtonController/StartGameButton</t>
   </si>
 </sst>
 </file>
@@ -283,12 +287,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -626,6 +636,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{534BB608-6D57-4BDE-A35C-F59C47044D40}">
   <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="14.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" customWidth="1"/>
+    <col min="6" max="6" width="23.75" customWidth="1"/>
+    <col min="7" max="7" width="50.6640625" customWidth="1"/>
+    <col min="8" max="8" width="28.1640625" customWidth="1"/>
+    <col min="9" max="9" width="29.75" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="11" max="11" width="29.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.9140625" customWidth="1"/>
+    <col min="13" max="13" width="21.25" customWidth="1"/>
+    <col min="14" max="14" width="22.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.9140625" customWidth="1"/>
+    <col min="18" max="18" width="20.58203125" customWidth="1"/>
+    <col min="19" max="19" width="21.6640625" customWidth="1"/>
+    <col min="20" max="20" width="19.4140625" customWidth="1"/>
+    <col min="21" max="21" width="25.08203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -634,7 +663,7 @@
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -699,7 +728,7 @@
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -764,7 +793,7 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -826,62 +855,60 @@
       <c r="B4">
         <v>100101</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>1001</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="L4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/TutorialStepData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/TutorialStepData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCC9928-128E-4992-9BA5-C2929377B67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12455A6-27C0-4726-8E67-2092638079DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16370" yWindow="7300" windowWidth="44100" windowHeight="18570" xr2:uid="{2289B342-06D8-41FC-9CAA-D2C17ACF82D3}"/>
+    <workbookView xWindow="-2510" yWindow="6400" windowWidth="44100" windowHeight="18570" xr2:uid="{2289B342-06D8-41FC-9CAA-D2C17ACF82D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -235,22 +235,45 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MainUI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>模板行:高亮大厅的背包按钮,点中它这段引导就结束</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UIMask/MenuButtonController/StartGameButton</t>
+  </si>
+  <si>
+    <t>CommonUI</t>
+  </si>
+  <si>
+    <t>HandPosition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指引图标的位置(x,y),屏幕中心为原点,编辑器里摆好直接抄Inspector的Pos X/Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>-674</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,82</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +284,13 @@
     <font>
       <sz val="9"/>
       <name val="Consolas"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -634,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{534BB608-6D57-4BDE-A35C-F59C47044D40}">
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.5" style="3" customWidth="1"/>
@@ -644,19 +674,20 @@
     <col min="7" max="7" width="50.6640625" customWidth="1"/>
     <col min="8" max="8" width="28.1640625" customWidth="1"/>
     <col min="9" max="9" width="29.75" customWidth="1"/>
-    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="38.4140625" customWidth="1"/>
     <col min="11" max="11" width="29.83203125" customWidth="1"/>
     <col min="12" max="12" width="24.9140625" customWidth="1"/>
     <col min="13" max="13" width="21.25" customWidth="1"/>
     <col min="14" max="14" width="22.33203125" customWidth="1"/>
     <col min="17" max="17" width="18.9140625" customWidth="1"/>
-    <col min="18" max="18" width="20.58203125" customWidth="1"/>
-    <col min="19" max="19" width="21.6640625" customWidth="1"/>
-    <col min="20" max="20" width="19.4140625" customWidth="1"/>
-    <col min="21" max="21" width="25.08203125" customWidth="1"/>
+    <col min="18" max="18" width="34.9140625" customWidth="1"/>
+    <col min="19" max="19" width="20.58203125" customWidth="1"/>
+    <col min="20" max="20" width="43.6640625" customWidth="1"/>
+    <col min="21" max="21" width="19.4140625" customWidth="1"/>
+    <col min="22" max="22" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -709,19 +740,22 @@
         <v>42</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -774,19 +808,22 @@
         <v>43</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -839,19 +876,22 @@
         <v>44</v>
       </c>
       <c r="R3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>100101</v>
       </c>
@@ -865,10 +905,10 @@
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
@@ -896,19 +936,22 @@
         <v>62</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="R4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="U4" s="1" t="s">
-        <v>65</v>
+      <c r="V4" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/TutorialStepData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/TutorialStepData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12455A6-27C0-4726-8E67-2092638079DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57170D49-AEBF-4726-A3EE-2DDD0EDED69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2510" yWindow="6400" windowWidth="44100" windowHeight="18570" xr2:uid="{2289B342-06D8-41FC-9CAA-D2C17ACF82D3}"/>
+    <workbookView xWindow="1470" yWindow="5350" windowWidth="44100" windowHeight="18570" xr2:uid="{2289B342-06D8-41FC-9CAA-D2C17ACF82D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -204,9 +204,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>UIPath</t>
   </si>
   <si>
     <t/>
@@ -237,12 +234,6 @@
   <si>
     <t>模板行:高亮大厅的背包按钮,点中它这段引导就结束</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIMask/MenuButtonController/StartGameButton</t>
-  </si>
-  <si>
-    <t>CommonUI</t>
   </si>
   <si>
     <t>HandPosition</t>
@@ -266,6 +257,14 @@
       </rPr>
       <t>,82</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial/Step_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -678,7 +677,7 @@
     <col min="11" max="11" width="29.83203125" customWidth="1"/>
     <col min="12" max="12" width="24.9140625" customWidth="1"/>
     <col min="13" max="13" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="22.33203125" customWidth="1"/>
+    <col min="14" max="14" width="43.25" customWidth="1"/>
     <col min="17" max="17" width="18.9140625" customWidth="1"/>
     <col min="18" max="18" width="34.9140625" customWidth="1"/>
     <col min="19" max="19" width="20.58203125" customWidth="1"/>
@@ -740,7 +739,7 @@
         <v>42</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>45</v>
@@ -876,7 +875,7 @@
         <v>44</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>47</v>
@@ -892,7 +891,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B4">
+      <c r="B4" s="3">
         <v>100101</v>
       </c>
       <c r="C4" s="3">
@@ -902,56 +901,52 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>65</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="P4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q4">
         <v>270</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="V4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
